--- a/Archivos/Excel/ModeloEnriquecido.xlsx
+++ b/Archivos/Excel/ModeloEnriquecido.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29301"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DrOkt\OneDrive\Documents\CogniCare - Raz. Cuantitativo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DrOkt\Documents\GitHub\Documentacion_CC_RazCuantitativo\Archivos\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{396A8225-4837-42AE-98FC-FC83F41750B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9730D997-65E1-47E0-BF89-312EE7E883A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{36012E7C-B3F4-482B-AC16-7CCB81B9AE88}"/>
+    <workbookView xWindow="8445" yWindow="0" windowWidth="20355" windowHeight="15600" activeTab="1" xr2:uid="{36012E7C-B3F4-482B-AC16-7CCB81B9AE88}"/>
   </bookViews>
   <sheets>
     <sheet name="Modelo dominio anémico contexto" sheetId="61" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Nivel" sheetId="73" r:id="rId8"/>
     <sheet name="Estimulo" sheetId="74" r:id="rId9"/>
     <sheet name="Opciones de Respuesta" sheetId="76" r:id="rId10"/>
+    <sheet name="Respuestas Correctas" sheetId="78" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Listado Objetos de Dominio'!$A$2:$B$2</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="245">
   <si>
     <t>Subdominio/Contexto:</t>
   </si>
@@ -224,9 +225,6 @@
     <t>estimuloId</t>
   </si>
   <si>
-    <t>Identificador único del estimulo.</t>
-  </si>
-  <si>
     <t>intentos</t>
   </si>
   <si>
@@ -323,9 +321,6 @@
     <t>Mostrar mensaje de error y solicitar datos nuevamente.</t>
   </si>
   <si>
-    <t>estimuloIdNoVacio</t>
-  </si>
-  <si>
     <t>Validar que el estimulo existe.</t>
   </si>
   <si>
@@ -623,9 +618,6 @@
     <t>Requerido para crear un estimulo.</t>
   </si>
   <si>
-    <t>Identificador de la tarea asociada.</t>
-  </si>
-  <si>
     <t>Identificador del nivel asociado.</t>
   </si>
   <si>
@@ -668,12 +660,6 @@
     <t>Estimulo existente.</t>
   </si>
   <si>
-    <t>tareaEstimuloExiste</t>
-  </si>
-  <si>
-    <t>Validar que el estimulo este vinculado a una tarea.</t>
-  </si>
-  <si>
     <t>nivelEstimuloExiste</t>
   </si>
   <si>
@@ -731,12 +717,6 @@
     <t>Orden de opcion en que se ubica esta opcion.</t>
   </si>
   <si>
-    <t>detalle</t>
-  </si>
-  <si>
-    <t>Descripcion de la opcion.</t>
-  </si>
-  <si>
     <t>Estimulo y Opción</t>
   </si>
   <si>
@@ -774,13 +754,43 @@
   </si>
   <si>
     <t>Opción no existente.</t>
+  </si>
+  <si>
+    <t>Respuestas Correctas</t>
+  </si>
+  <si>
+    <t>Cada opcion de respuesta que sea correcta.</t>
+  </si>
+  <si>
+    <t>opcionId</t>
+  </si>
+  <si>
+    <t>Identificador único del opcion de respuesta.</t>
+  </si>
+  <si>
+    <t>opcionIdNoVacio</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>Indice de la tarea.</t>
+  </si>
+  <si>
+    <t>Puntos dados por el estímulo.</t>
+  </si>
+  <si>
+    <t>Identificador de la opcion de respuesta específico.</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1283,7 +1293,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1494,6 +1504,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1506,6 +1525,36 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1518,15 +1567,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1548,29 +1591,44 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1599,44 +1657,38 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1653,45 +1705,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1706,6 +1725,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1737,22 +1768,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>73959</xdr:colOff>
+      <xdr:colOff>66675</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>75640</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>350184</xdr:colOff>
+      <xdr:colOff>638175</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>180415</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A5DB019-00EC-EBC1-7CC1-6F5B61922AD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54ADFD6C-A7C5-9A3D-D45C-CE9C3B97689B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1774,8 +1805,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="73959" y="75640"/>
-          <a:ext cx="6372225" cy="5248275"/>
+          <a:off x="66675" y="66675"/>
+          <a:ext cx="6667500" cy="5248275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1788,9 +1819,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1828,7 +1859,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1934,7 +1965,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2076,7 +2107,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2085,12 +2116,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EFF4C49-240B-4036-BD62-669D42F23E67}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1"/>
     </row>
   </sheetData>
@@ -2102,8 +2133,8 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88DE883-41D6-4BA5-9557-BE7D27274C8C}">
-  <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2127,73 +2158,73 @@
     <col min="20" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$9</f>
         <v>Opciones de Respuesta</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="139" t="str">
+      <c r="B3" s="128" t="str">
         <f>'Listado Objetos de Dominio'!$B$9</f>
         <v>Cada opcion de respuesta única de un estimulo.</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="139"/>
-      <c r="P3" s="139"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -2243,15 +2274,15 @@
         <v>3</v>
       </c>
       <c r="Q4" s="30" t="str">
-        <f>A16</f>
+        <f>A15</f>
         <v>crearOpcion</v>
       </c>
       <c r="R4" s="29" t="str">
-        <f>A19</f>
+        <f>A17</f>
         <v>eliminarOpcion</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -2270,7 +2301,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -2288,16 +2321,16 @@
         <v>48</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q5" s="28" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="R5" s="22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>57</v>
       </c>
@@ -2334,31 +2367,37 @@
         <v>49</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+        <v>244</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>50</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4">
         <v>1</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="I7" s="148" t="s">
+        <v>240</v>
+      </c>
       <c r="J7" s="12"/>
       <c r="K7" s="11" t="s">
         <v>49</v>
@@ -2376,329 +2415,719 @@
         <v>49</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="R7" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88" t="s">
+        <v>75</v>
+      </c>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88" t="s">
+        <v>76</v>
+      </c>
+      <c r="R13" s="95"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="89"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="90" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R14" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="107" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="108"/>
+      <c r="C15" s="129" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="J15" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="129" t="s">
+        <v>175</v>
+      </c>
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="101" t="s">
         <v>227</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>500</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="P8" s="6" t="s">
+      <c r="P15" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="Q8" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="R8" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="10" spans="1:18">
-      <c r="A10" s="95" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="97"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="62.25" customHeight="1" thickBot="1">
-      <c r="A12" s="46" t="s">
+      <c r="Q15" s="101" t="s">
         <v>229</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="R15" s="141" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="109"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="J16" s="140"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="135"/>
+      <c r="P16" s="135"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="142"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="149" t="s">
         <v>230</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="B17" s="150"/>
+      <c r="C17" s="119" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="14" spans="1:18">
-      <c r="A14" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82" t="s">
-        <v>75</v>
-      </c>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="R14" s="83"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="99"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="84" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="P15" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="R15" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="113" t="s">
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="114"/>
-      <c r="C16" s="127" t="s">
+      <c r="P17" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="D16" s="128"/>
-      <c r="E16" s="128"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="47" t="s">
-        <v>189</v>
-      </c>
-      <c r="J16" s="122" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" s="127" t="s">
-        <v>177</v>
-      </c>
-      <c r="L16" s="128"/>
-      <c r="M16" s="128"/>
-      <c r="N16" s="129"/>
-      <c r="O16" s="90" t="s">
+      <c r="Q17" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="P16" s="90" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q16" s="90" t="s">
-        <v>236</v>
-      </c>
-      <c r="R16" s="133" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="115"/>
-      <c r="B17" s="116"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="47" t="s">
-        <v>226</v>
-      </c>
-      <c r="J17" s="126"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="135"/>
-      <c r="P17" s="135"/>
-      <c r="Q17" s="135"/>
-      <c r="R17" s="134"/>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="115"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="J18" s="126"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="131"/>
-      <c r="M18" s="131"/>
-      <c r="N18" s="132"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="135"/>
-      <c r="Q18" s="135"/>
-      <c r="R18" s="134"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="136" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="137"/>
-      <c r="C19" s="138" t="s">
-        <v>238</v>
-      </c>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J19" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K19" s="138" t="s">
-        <v>98</v>
-      </c>
-      <c r="L19" s="138"/>
-      <c r="M19" s="138"/>
-      <c r="N19" s="138"/>
-      <c r="O19" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="P19" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q19" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="R19" s="25" t="s">
-        <v>102</v>
+      <c r="R17" s="25" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:F16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:P3"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:F15"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="A16:B18"/>
-    <mergeCell ref="C16:F18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="K16:N18"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="Q16:Q18"/>
-    <mergeCell ref="R16:R18"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:F14"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:P13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{E3ECF641-1F8C-4BA7-A67E-39F08CEDBDC7}"/>
     <hyperlink ref="R4" location="'Opciones de Respuesta'!A19" display="'Opciones de Respuesta'!A19" xr:uid="{E586584F-7BEA-4E70-A6CE-4FE4813E5290}"/>
-    <hyperlink ref="A19:B19" location="'Opciones de Respuesta'!R4" display="eliminarOpcion" xr:uid="{A372F582-9279-4A7E-92BD-65DB7BC6BCA5}"/>
-    <hyperlink ref="A16:B16" location="'Objeto Dominio N'!Q4" display="Reponsabilidad 1" xr:uid="{5C8DCCF1-EB53-4AD5-952C-C6270DB1617D}"/>
+    <hyperlink ref="A17:B17" location="'Opciones de Respuesta'!R4" display="eliminarOpcion" xr:uid="{A372F582-9279-4A7E-92BD-65DB7BC6BCA5}"/>
+    <hyperlink ref="A15:B15" location="'Objeto Dominio N'!Q4" display="Reponsabilidad 1" xr:uid="{5C8DCCF1-EB53-4AD5-952C-C6270DB1617D}"/>
     <hyperlink ref="Q4" location="'Opciones de Respuesta'!A16" display="'Opciones de Respuesta'!A16" xr:uid="{91B96BA8-AB2D-4113-8816-CC2AC73F5315}"/>
     <hyperlink ref="A1:P1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{8BE478EA-F497-44CF-8E44-A26EEC82A896}"/>
-    <hyperlink ref="A16:B18" location="'Opciones de Respuesta'!Q4" display="crearOpcion" xr:uid="{C6B565AD-CE0E-478D-84E0-D9FDD8EE743E}"/>
+    <hyperlink ref="A15:B16" location="'Opciones de Respuesta'!Q4" display="crearOpcion" xr:uid="{C6B565AD-CE0E-478D-84E0-D9FDD8EE743E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF581A91-97A0-49B0-906D-3768F53F8793}">
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="79.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="94.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="132.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="46.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="52.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="82" t="str">
+        <f>'Listado Objetos de Dominio'!$A$9</f>
+        <v>Opciones de Respuesta</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="128" t="str">
+        <f>'Listado Objetos de Dominio'!$B$9</f>
+        <v>Cada opcion de respuesta única de un estimulo.</v>
+      </c>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="R4" s="29" t="str">
+        <f>A15</f>
+        <v>eliminarOpcion</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="4">
+        <v>36</v>
+      </c>
+      <c r="D5" s="4">
+        <v>36</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="R5" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4">
+        <v>36</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q6" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="R6" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="88"/>
+      <c r="L12" s="88"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="88"/>
+      <c r="O12" s="88" t="s">
+        <v>75</v>
+      </c>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88" t="s">
+        <v>76</v>
+      </c>
+      <c r="R12" s="95"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="89"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="90" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R13" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="151" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14" s="110"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="J14" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="132" t="s">
+        <v>175</v>
+      </c>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="134"/>
+      <c r="O14" s="74" t="s">
+        <v>227</v>
+      </c>
+      <c r="P14" s="74" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q14" s="74" t="s">
+        <v>229</v>
+      </c>
+      <c r="R14" s="76" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="149" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="150"/>
+      <c r="C15" s="119" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="120"/>
+      <c r="M15" s="120"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="R15" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:F13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:P12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{91354C3E-C2E7-4DEA-A583-12061118BBA5}"/>
+    <hyperlink ref="R4" location="'Respuesta Correcta'!A15" display="'Respuesta Correcta'!A15" xr:uid="{761C0363-9E94-4388-B6F9-B81E9DC92972}"/>
+    <hyperlink ref="A15:B15" location="'Respuesta Correcta'!R4" display="eliminarOpcion" xr:uid="{C8486F4A-3347-4658-A7D6-170DFBFD7C10}"/>
+    <hyperlink ref="Q4" location="'Respuesta Correcta'!A16" display="crearOpcion" xr:uid="{D964FF7B-677C-40E2-AF75-91434386577C}"/>
+    <hyperlink ref="A1:P1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{126090F0-C986-4C6C-8C49-1CB872CB741B}"/>
+    <hyperlink ref="A14:B14" location="'Respuesta Correcta'!Q4" display="'Respuesta Correcta'!Q4" xr:uid="{BB305DAF-270E-49F1-A4DA-C433D344955A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2707,8 +3136,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02388B9D-0652-49D5-BF62-A59B793D6DFC}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2717,17 +3146,17 @@
     <col min="5" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="75"/>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="C1" s="77"/>
+      <c r="D1" s="78"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
         <v>2</v>
       </c>
@@ -2741,7 +3170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30">
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
         <v>6</v>
       </c>
@@ -2755,7 +3184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30">
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="71" t="s">
         <v>10</v>
       </c>
@@ -2769,7 +3198,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30">
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
         <v>12</v>
       </c>
@@ -2783,7 +3212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="71" t="s">
         <v>14</v>
       </c>
@@ -2797,7 +3226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30">
+    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
         <v>16</v>
       </c>
@@ -2811,7 +3240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30">
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
         <v>18</v>
       </c>
@@ -2825,17 +3254,31 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30.75" thickBot="1">
-      <c r="A9" s="72" t="s">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="72" t="s">
+        <v>235</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="49" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2851,6 +3294,7 @@
     <hyperlink ref="A9" location="'Opciones de Respuesta'!A1" display="Opciones de Respuesta" xr:uid="{221005B4-BAAF-4A9A-95B2-A310AFB2EF80}"/>
     <hyperlink ref="A6" location="Tarea!A1" display="Tarea" xr:uid="{179E6993-B368-4856-88F1-B880B42989B8}"/>
     <hyperlink ref="A5" location="Tutorial!A1" display="Tutorial" xr:uid="{B139B732-F438-4515-83AF-9C183A300B13}"/>
+    <hyperlink ref="A10" location="'Respuestas Correctas'!A1" display="Respuestas Correctas" xr:uid="{94B2281A-3D20-42F7-9DEC-40F3BB4A76DD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2872,19 +3316,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D2CB1A-ACAF-48CA-A6AD-4DD0D3A676EA}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="77"/>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="B1" s="80"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>4</v>
       </c>
@@ -2892,7 +3336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
         <v>8</v>
       </c>
@@ -2900,7 +3344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" thickBot="1">
+    <row r="4" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="38" t="s">
         <v>24</v>
       </c>
@@ -2919,7 +3363,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC3248D-1B82-4DA6-94D4-6217A3463E15}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2943,73 +3387,73 @@
     <col min="20" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$3</f>
         <v>Respuesta Estimulo</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="94" t="str">
+      <c r="B3" s="83" t="str">
         <f>'Listado Objetos de Dominio'!$B$3</f>
         <v>Respuestas del estudiante por cada estímulo durante una sesión.</v>
       </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -3066,7 +3510,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -3085,7 +3529,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -3112,7 +3558,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>53</v>
       </c>
@@ -3158,9 +3604,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>46</v>
@@ -3195,7 +3641,7 @@
         <v>49</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>58</v>
+        <v>238</v>
       </c>
       <c r="Q7" s="28" t="s">
         <v>55</v>
@@ -3204,12 +3650,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -3239,7 +3685,7 @@
         <v>49</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q8" s="28" t="s">
         <v>55</v>
@@ -3248,12 +3694,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -3265,9 +3711,7 @@
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="12"/>
       <c r="K9" s="11" t="s">
         <v>49</v>
@@ -3285,7 +3729,7 @@
         <v>49</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="28" t="s">
         <v>55</v>
@@ -3294,12 +3738,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -3309,9 +3753,7 @@
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
+      <c r="I10" s="4"/>
       <c r="J10" s="12"/>
       <c r="K10" s="11" t="s">
         <v>49</v>
@@ -3329,7 +3771,7 @@
         <v>49</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q10" s="28" t="s">
         <v>55</v>
@@ -3338,81 +3780,81 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="12" spans="1:18">
-      <c r="A12" s="95" t="s">
+    <row r="11" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="85"/>
+      <c r="C12" s="86"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="97"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="68.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="68.25" customHeight="1" thickBot="1">
-      <c r="A14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="C14" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="31" t="s">
+    </row>
+    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="87" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="16" spans="1:18">
-      <c r="A16" s="98" t="s">
+      <c r="B16" s="88"/>
+      <c r="C16" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82" t="s">
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82" t="s">
+      <c r="K16" s="88"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82" t="s">
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="82" t="s">
+      <c r="R16" s="95"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="89"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="R16" s="83"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="99"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="18" t="s">
+      <c r="H17" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>3</v>
@@ -3420,36 +3862,36 @@
       <c r="J17" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="K17" s="84" t="s">
+      <c r="K17" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="84"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="90"/>
       <c r="O17" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P17" s="18" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R17" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R17" s="24" t="s">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="97" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="86" t="s">
+      <c r="B18" s="98"/>
+      <c r="C18" s="96" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="96"/>
       <c r="G18" s="19" t="s">
         <v>53</v>
       </c>
@@ -3459,155 +3901,155 @@
       <c r="I18" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="78" t="s">
+      <c r="J18" s="91" t="s">
+        <v>84</v>
+      </c>
+      <c r="K18" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="85" t="s">
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="L18" s="85"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="19" t="s">
+      <c r="P18" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="P18" s="19" t="s">
+      <c r="Q18" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="Q18" s="89" t="s">
+      <c r="R18" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="R18" s="88" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="86"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="97"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="96"/>
       <c r="G19" s="19" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>46</v>
       </c>
       <c r="I19" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" s="91"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="100"/>
+      <c r="R19" s="99"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="97"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="19" t="s">
+      <c r="H20" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" s="91"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="P19" s="19" t="s">
+      <c r="P20" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="88"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="19" t="s">
+      <c r="Q20" s="100"/>
+      <c r="R20" s="99"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="97"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="91"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="96"/>
+      <c r="O21" s="101" t="s">
+        <v>93</v>
+      </c>
+      <c r="P21" s="101" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q21" s="100"/>
+      <c r="R21" s="99"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="97"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H20" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="85"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="88"/>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="86"/>
-      <c r="B21" s="87"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="I21" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="78"/>
-      <c r="K21" s="85"/>
-      <c r="L21" s="85"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="90" t="s">
+      <c r="I22" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="J22" s="91"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="96"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="102"/>
+      <c r="Q22" s="100"/>
+      <c r="R22" s="99"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="92" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="93"/>
+      <c r="C23" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="P21" s="90" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="88"/>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="86"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="J22" s="78"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="85"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="91"/>
-      <c r="Q22" s="89"/>
-      <c r="R22" s="88"/>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="81" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="94"/>
       <c r="G23" s="22" t="s">
         <v>45</v>
       </c>
@@ -3618,38 +4060,29 @@
         <v>50</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="K23" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="K23" s="94" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="94"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
+      <c r="O23" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="P23" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="22" t="s">
+      <c r="Q23" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="P23" s="23" t="s">
+      <c r="R23" s="25" t="s">
         <v>100</v>
-      </c>
-      <c r="Q23" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="R23" s="25" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:F17"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:N16"/>
-    <mergeCell ref="O16:P16"/>
     <mergeCell ref="J18:J22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:F23"/>
@@ -3663,6 +4096,15 @@
     <mergeCell ref="K18:N22"/>
     <mergeCell ref="O21:O22"/>
     <mergeCell ref="P21:P22"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:F17"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:N16"/>
+    <mergeCell ref="O16:P16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{D2337650-12B8-4597-96E2-02FCCADF338D}"/>
@@ -3681,7 +4123,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA408A11-E9A3-49F4-8402-6C6AAC9767EC}">
   <dimension ref="A1:T23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -3706,73 +4148,73 @@
     <col min="21" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$4</f>
         <v>Tutorial Tarea</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="94" t="str">
+      <c r="B3" s="83" t="str">
         <f>'Listado Objetos de Dominio'!$B$4</f>
         <v>Serie de instrucciones sobre como funciona la tarea antes de la sesión. Representada por un cerebrito de caricatura.</v>
       </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -3822,10 +4264,10 @@
         <v>3</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S4" s="64" t="str">
         <f>A22</f>
@@ -3836,7 +4278,7 @@
         <v>finalizarTutorial</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -3855,7 +4297,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -3873,13 +4317,13 @@
         <v>48</v>
       </c>
       <c r="P5" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="R5" s="22" t="s">
         <v>105</v>
-      </c>
-      <c r="Q5" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="R5" s="22" t="s">
-        <v>107</v>
       </c>
       <c r="S5" s="65" t="s">
         <v>56</v>
@@ -3888,12 +4332,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -3923,10 +4367,10 @@
         <v>49</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>56</v>
@@ -3938,12 +4382,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -3954,7 +4398,7 @@
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="4" t="s">
@@ -3973,24 +4417,24 @@
         <v>49</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R7" s="22" t="s">
         <v>56</v>
       </c>
       <c r="S7" s="65" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T7" s="61" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>46</v>
@@ -4025,10 +4469,10 @@
         <v>49</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q8" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R8" s="22" t="s">
         <v>56</v>
@@ -4040,12 +4484,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -4053,7 +4497,9 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="I9" s="4">
+        <v>5</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="4" t="s">
         <v>49</v>
@@ -4071,10 +4517,10 @@
         <v>49</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q9" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R9" s="22" t="s">
         <v>56</v>
@@ -4086,81 +4532,81 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" thickBot="1"/>
-    <row r="11" spans="1:20">
-      <c r="A11" s="95" t="s">
+    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="86"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="97"/>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="81.75" customHeight="1" thickBot="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="81.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15.75" thickBot="1"/>
-    <row r="15" spans="1:20">
-      <c r="A15" s="98" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82" t="s">
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82" t="s">
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82" t="s">
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82" t="s">
+      <c r="R15" s="95"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="89"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="R15" s="83"/>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="99"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="18" t="s">
+      <c r="H16" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>3</v>
@@ -4168,170 +4614,170 @@
       <c r="J16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="K16" s="84" t="s">
+      <c r="K16" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
       <c r="O16" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P16" s="18" t="s">
         <v>3</v>
       </c>
       <c r="Q16" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R16" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R16" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="112" t="s">
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="107" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="108"/>
+      <c r="C17" s="106" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="47" t="s">
+      <c r="P17" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q17" s="100" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" s="122" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="109"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="78" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="28" t="s">
+      <c r="H18" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="91"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="P17" s="52" t="s">
+      <c r="P18" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="Q17" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="R17" s="106" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="115"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="47" t="s">
+      <c r="Q18" s="100"/>
+      <c r="R18" s="123"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="109"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="28" t="s">
         <v>113</v>
-      </c>
-      <c r="J18" s="78"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="85"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="P18" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="107"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="115"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="28" t="s">
-        <v>115</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>46</v>
       </c>
       <c r="I19" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="91"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q19" s="100" t="s">
+        <v>127</v>
+      </c>
+      <c r="R19" s="123"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="111"/>
+      <c r="B20" s="112"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="P19" s="52" t="s">
+      <c r="J20" s="91"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="Q19" s="89" t="s">
+      <c r="P20" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="R19" s="107"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="117"/>
-      <c r="B20" s="118"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="85"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="28" t="s">
+      <c r="Q20" s="100"/>
+      <c r="R20" s="124"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="68"/>
+      <c r="C21" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="P20" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="108"/>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A21" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="119" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="121"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="53" t="s">
         <v>45</v>
       </c>
@@ -4339,95 +4785,95 @@
         <v>46</v>
       </c>
       <c r="I21" s="54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J21" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="K21" s="103" t="s">
-        <v>98</v>
-      </c>
-      <c r="L21" s="104"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="105"/>
+        <v>84</v>
+      </c>
+      <c r="K21" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="120"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="121"/>
       <c r="O21" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="P21" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q21" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="P21" s="23" t="s">
+      <c r="R21" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="Q21" s="33" t="s">
+      <c r="B22" s="117"/>
+      <c r="C22" s="118" t="s">
         <v>135</v>
       </c>
-      <c r="R21" s="25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="30">
-      <c r="A22" s="100" t="s">
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="118" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="101"/>
-      <c r="C22" s="102" t="s">
+      <c r="L22" s="118"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="K22" s="102" t="s">
+      <c r="P22" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="L22" s="102"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="26" t="s">
+      <c r="Q22" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="P22" s="26" t="s">
+      <c r="R22" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="Q22" s="26" t="s">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="103" t="s">
         <v>141</v>
       </c>
-      <c r="R22" s="57" t="s">
+      <c r="B23" s="104"/>
+      <c r="C23" s="105" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="109" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="111" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
       <c r="G23" s="59"/>
       <c r="H23" s="60"/>
       <c r="I23" s="58"/>
       <c r="J23" s="59" t="s">
-        <v>85</v>
-      </c>
-      <c r="K23" s="111" t="s">
-        <v>145</v>
-      </c>
-      <c r="L23" s="111"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="111"/>
+        <v>84</v>
+      </c>
+      <c r="K23" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
       <c r="O23" s="61"/>
       <c r="P23" s="62"/>
       <c r="Q23" s="62"/>
@@ -4435,6 +4881,17 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="K17:N20"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="R17:R20"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="K23:N23"/>
@@ -4450,17 +4907,6 @@
     <mergeCell ref="C17:F20"/>
     <mergeCell ref="A17:B20"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="J17:J20"/>
-    <mergeCell ref="K17:N20"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="R17:R20"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="Q19:Q20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{619D6E1B-54D9-44EE-9C0E-E16784A82EA2}"/>
@@ -4482,7 +4928,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7622914C-1CBD-4C18-9D04-3FC32D963659}">
   <dimension ref="A1:T23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -4507,73 +4953,73 @@
     <col min="21" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$5</f>
         <v>Tutorial Nivel</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="94" t="str">
+      <c r="B3" s="83" t="str">
         <f>'Listado Objetos de Dominio'!$B$5</f>
         <v>Serie de instrucciones sobre como funciona un nivel antes de la sesión. Representada por un cerebrito de caricatura.</v>
       </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="94"/>
-      <c r="P3" s="94"/>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -4623,10 +5069,10 @@
         <v>3</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S4" s="64" t="str">
         <f>A22</f>
@@ -4637,7 +5083,7 @@
         <v>finalizarTutorial</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -4656,7 +5102,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -4674,13 +5122,13 @@
         <v>48</v>
       </c>
       <c r="P5" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q5" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="R5" s="22" t="s">
         <v>105</v>
-      </c>
-      <c r="Q5" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="R5" s="22" t="s">
-        <v>107</v>
       </c>
       <c r="S5" s="65" t="s">
         <v>56</v>
@@ -4689,12 +5137,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -4706,7 +5154,9 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="148" t="s">
+        <v>240</v>
+      </c>
       <c r="J6" s="12"/>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -4724,10 +5174,10 @@
         <v>49</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>56</v>
@@ -4739,12 +5189,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -4754,9 +5204,7 @@
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
+      <c r="I7" s="4"/>
       <c r="J7" s="5"/>
       <c r="K7" s="4" t="s">
         <v>49</v>
@@ -4774,24 +5222,24 @@
         <v>49</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R7" s="22" t="s">
         <v>56</v>
       </c>
       <c r="S7" s="65" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T7" s="61" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>46</v>
@@ -4826,10 +5274,10 @@
         <v>49</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q8" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R8" s="22" t="s">
         <v>56</v>
@@ -4841,12 +5289,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -4854,7 +5302,9 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="I9" s="4">
+        <v>5</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="4" t="s">
         <v>49</v>
@@ -4872,10 +5322,10 @@
         <v>49</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q9" s="28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R9" s="22" t="s">
         <v>56</v>
@@ -4887,81 +5337,81 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.75" thickBot="1"/>
-    <row r="11" spans="1:20">
-      <c r="A11" s="95" t="s">
+    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="86"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="97"/>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="81.75" customHeight="1" thickBot="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="81.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15.75" thickBot="1"/>
-    <row r="15" spans="1:20">
-      <c r="A15" s="98" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82" t="s">
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82" t="s">
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82" t="s">
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82" t="s">
+      <c r="R15" s="95"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="89"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="R15" s="83"/>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="99"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="18" t="s">
+      <c r="H16" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>3</v>
@@ -4969,170 +5419,170 @@
       <c r="J16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="K16" s="84" t="s">
+      <c r="K16" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
       <c r="O16" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P16" s="18" t="s">
         <v>3</v>
       </c>
       <c r="Q16" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R16" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R16" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15" customHeight="1">
-      <c r="A17" s="113" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="112" t="s">
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="107" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="108"/>
+      <c r="C17" s="106" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="47" t="s">
+      <c r="P17" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q17" s="100" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" s="122" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="109"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="78" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="28" t="s">
+      <c r="H18" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="91"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="96"/>
+      <c r="O18" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="P17" s="52" t="s">
+      <c r="P18" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="Q17" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="R17" s="106" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="115"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="112"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="78"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="85"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="P18" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="107"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="115"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="123"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="109"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
       <c r="G19" s="28" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>46</v>
       </c>
       <c r="I19" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="91"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="96"/>
+      <c r="O19" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q19" s="100" t="s">
+        <v>127</v>
+      </c>
+      <c r="R19" s="123"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="111"/>
+      <c r="B20" s="112"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="P19" s="52" t="s">
+      <c r="J20" s="91"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="Q19" s="89" t="s">
+      <c r="P20" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="R19" s="107"/>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="117"/>
-      <c r="B20" s="118"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="J20" s="78"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="85"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="28" t="s">
+      <c r="Q20" s="100"/>
+      <c r="R20" s="124"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="68"/>
+      <c r="C21" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="P20" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="108"/>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A21" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="119" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
-      <c r="F21" s="121"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
       <c r="G21" s="53" t="s">
         <v>45</v>
       </c>
@@ -5140,95 +5590,95 @@
         <v>46</v>
       </c>
       <c r="I21" s="54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J21" s="55" t="s">
-        <v>85</v>
-      </c>
-      <c r="K21" s="103" t="s">
-        <v>98</v>
-      </c>
-      <c r="L21" s="104"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="105"/>
+        <v>84</v>
+      </c>
+      <c r="K21" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="120"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="121"/>
       <c r="O21" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="P21" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q21" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="P21" s="23" t="s">
+      <c r="R21" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="Q21" s="33" t="s">
+      <c r="B22" s="117"/>
+      <c r="C22" s="118" t="s">
         <v>135</v>
       </c>
-      <c r="R21" s="25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="30">
-      <c r="A22" s="100" t="s">
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="118" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="101"/>
-      <c r="C22" s="102" t="s">
+      <c r="L22" s="118"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="102"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="K22" s="102" t="s">
+      <c r="P22" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="L22" s="102"/>
-      <c r="M22" s="102"/>
-      <c r="N22" s="102"/>
-      <c r="O22" s="26" t="s">
+      <c r="Q22" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="P22" s="26" t="s">
+      <c r="R22" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="Q22" s="26" t="s">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="103" t="s">
         <v>141</v>
       </c>
-      <c r="R22" s="57" t="s">
+      <c r="B23" s="104"/>
+      <c r="C23" s="105" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="109" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="111" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
       <c r="G23" s="59"/>
       <c r="H23" s="60"/>
       <c r="I23" s="58"/>
       <c r="J23" s="59" t="s">
-        <v>85</v>
-      </c>
-      <c r="K23" s="111" t="s">
-        <v>145</v>
-      </c>
-      <c r="L23" s="111"/>
-      <c r="M23" s="111"/>
-      <c r="N23" s="111"/>
+        <v>84</v>
+      </c>
+      <c r="K23" s="105" t="s">
+        <v>143</v>
+      </c>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
       <c r="O23" s="61"/>
       <c r="P23" s="62"/>
       <c r="Q23" s="62"/>
@@ -5236,17 +5686,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:F16"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="K22:N22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="K23:N23"/>
@@ -5262,6 +5701,17 @@
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:F16"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="K22:N22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{0B91F1B8-5620-4211-9831-50A8865A18A3}"/>
@@ -5282,8 +5732,8 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB507482-0E70-42B1-A987-42284CFE0283}">
-  <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:R18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -5307,73 +5757,73 @@
     <col min="20" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$6</f>
         <v>Tarea</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="139" t="str">
+      <c r="B3" s="128" t="str">
         <f>'Listado Objetos de Dominio'!$B$6</f>
         <v>Serie de niveles y estímulos para que el entrenador evalúe las habilidades en razonamiento lógico del estudiante</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="139"/>
-      <c r="P3" s="139"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -5423,15 +5873,15 @@
         <v>3</v>
       </c>
       <c r="Q4" s="30" t="str">
-        <f>A14</f>
+        <f>A15</f>
         <v>crearTarea</v>
       </c>
       <c r="R4" s="29" t="str">
-        <f>A16</f>
+        <f>A17</f>
         <v>eliminarTarea</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -5450,7 +5900,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -5468,21 +5920,21 @@
         <v>48</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q5" s="28" t="s">
         <v>56</v>
       </c>
       <c r="R5" s="22" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -5494,7 +5946,9 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="148" t="s">
+        <v>240</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="4" t="s">
         <v>49</v>
@@ -5512,260 +5966,304 @@
         <v>49</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="8" spans="1:18">
-      <c r="A8" s="95" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="R7" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="97"/>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="16" t="s">
+      <c r="B10" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="15" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="76.5" customHeight="1" thickBot="1">
-      <c r="A10" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88" t="s">
+        <v>75</v>
+      </c>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88" t="s">
+        <v>76</v>
+      </c>
+      <c r="R13" s="95"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="89"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="90" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R14" s="24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="107" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="108"/>
+      <c r="C15" s="129" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="12" spans="1:18">
-      <c r="A12" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="R12" s="83"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="99"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="84" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="P13" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="R13" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="113" t="s">
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="101" t="s">
+        <v>147</v>
+      </c>
+      <c r="H15" s="136" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="138" t="s">
+        <v>148</v>
+      </c>
+      <c r="J15" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="129" t="s">
         <v>153</v>
       </c>
-      <c r="B14" s="114"/>
-      <c r="C14" s="127" t="s">
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="101" t="s">
         <v>154</v>
       </c>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="90" t="s">
-        <v>149</v>
-      </c>
-      <c r="H14" s="122" t="s">
-        <v>109</v>
-      </c>
-      <c r="I14" s="124" t="s">
-        <v>150</v>
-      </c>
-      <c r="J14" s="122" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" s="127" t="s">
+      <c r="P15" s="101" t="s">
         <v>155</v>
       </c>
-      <c r="L14" s="128"/>
-      <c r="M14" s="128"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="90" t="s">
+      <c r="Q15" s="101" t="s">
         <v>156</v>
       </c>
-      <c r="P14" s="90" t="s">
+      <c r="R15" s="141" t="s">
         <v>157</v>
       </c>
-      <c r="Q14" s="90" t="s">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="109"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="135"/>
+      <c r="P16" s="135"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="142"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="125" t="s">
         <v>158</v>
       </c>
-      <c r="R14" s="133" t="s">
+      <c r="B17" s="126"/>
+      <c r="C17" s="127" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="115"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="123"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="131"/>
-      <c r="N15" s="132"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="135"/>
-      <c r="Q15" s="135"/>
-      <c r="R15" s="134"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="136" t="s">
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="B16" s="137"/>
-      <c r="C16" s="138" t="s">
+      <c r="J17" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="K17" s="127" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="127"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="32" t="s">
+      <c r="P17" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="J16" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" s="138" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="138"/>
-      <c r="M16" s="138"/>
-      <c r="N16" s="138"/>
-      <c r="O16" s="22" t="s">
+      <c r="Q17" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="P16" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q16" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="R16" s="25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="69"/>
-      <c r="B17" s="69"/>
+      <c r="R17" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="69"/>
+      <c r="B18" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:N16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="K17:N17"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:P3"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:F13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="C14:F15"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:N15"/>
-    <mergeCell ref="R14:R15"/>
-    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:F14"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="C15:F16"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{1828DAD6-6F19-4554-84A9-74C7BB658A41}"/>
     <hyperlink ref="R4" location="Tarea!A16" display="Tarea!A16" xr:uid="{D31A6BD4-9960-4FF0-A4D3-367721E9650A}"/>
     <hyperlink ref="Q4" location="Tarea!A14" display="Tarea!A14" xr:uid="{38779614-C757-4B21-9109-4C5181968E0A}"/>
     <hyperlink ref="A1:P1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{A60EC94F-FFE3-48D1-B399-46FAEE979C38}"/>
-    <hyperlink ref="A16:B16" location="Tarea!R4" display="eliminarTarea" xr:uid="{D7B3B1FF-2A77-465D-A79E-8ACDAB3CA4FE}"/>
-    <hyperlink ref="A14:B14" location="'Objeto Dominio N'!Q4" display="Reponsabilidad 1" xr:uid="{03F2E601-D53B-483D-BDDB-8A425086DFE6}"/>
-    <hyperlink ref="A14:B15" location="Tarea!Q4" display="crearTarea" xr:uid="{CD7C64CA-2698-4FEF-8BB4-1BC01AA6EE4E}"/>
+    <hyperlink ref="A17:B17" location="Tarea!R4" display="eliminarTarea" xr:uid="{D7B3B1FF-2A77-465D-A79E-8ACDAB3CA4FE}"/>
+    <hyperlink ref="A15:B15" location="'Objeto Dominio N'!Q4" display="Reponsabilidad 1" xr:uid="{03F2E601-D53B-483D-BDDB-8A425086DFE6}"/>
+    <hyperlink ref="A15:B16" location="Tarea!Q4" display="crearTarea" xr:uid="{CD7C64CA-2698-4FEF-8BB4-1BC01AA6EE4E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5775,7 +6273,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B42DAB-B522-4956-AE20-8941EF312E98}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -5799,73 +6297,73 @@
     <col min="20" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$7</f>
         <v>Nivel</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="139" t="str">
+      <c r="B3" s="128" t="str">
         <f>'Listado Objetos de Dominio'!$B$7</f>
         <v>Subdivisión de una Tarea que aumenta progresivamente su dificultad</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="139"/>
-      <c r="P3" s="139"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -5923,7 +6421,7 @@
         <v>eliminarNivel</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -5942,7 +6440,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -5960,21 +6460,21 @@
         <v>48</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q5" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="R5" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="R5" s="22" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="10" t="s">
-        <v>168</v>
-      </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -5986,7 +6486,9 @@
         <v>3</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
       <c r="J6" s="12"/>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -6004,18 +6506,18 @@
         <v>49</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>46</v>
@@ -6050,90 +6552,90 @@
         <v>49</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R7" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="9" spans="1:18">
-      <c r="A9" s="95" t="s">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="97"/>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="86.25" customHeight="1" thickBot="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="86.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="13" spans="1:18">
-      <c r="A13" s="98" t="s">
+    </row>
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="88"/>
+      <c r="C13" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="88"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82" t="s">
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82" t="s">
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82" t="s">
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82" t="s">
+      <c r="R13" s="95"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="89"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="R13" s="83"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="99"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="18" t="s">
+      <c r="H14" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>3</v>
@@ -6141,104 +6643,104 @@
       <c r="J14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="K14" s="84" t="s">
+      <c r="K14" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="84"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="84"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
       <c r="O14" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P14" s="18" t="s">
         <v>3</v>
       </c>
       <c r="Q14" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R14" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R14" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="113" t="s">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="107" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="108"/>
+      <c r="C15" s="129" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="129" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="127" t="s">
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="101" t="s">
         <v>176</v>
       </c>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="J15" s="122" t="s">
-        <v>85</v>
-      </c>
-      <c r="K15" s="127" t="s">
+      <c r="P15" s="101" t="s">
         <v>177</v>
       </c>
-      <c r="L15" s="128"/>
-      <c r="M15" s="128"/>
-      <c r="N15" s="129"/>
-      <c r="O15" s="90" t="s">
+      <c r="Q15" s="101" t="s">
         <v>178</v>
       </c>
-      <c r="P15" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q15" s="90" t="s">
-        <v>180</v>
-      </c>
-      <c r="R15" s="133" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="117"/>
-      <c r="B16" s="118"/>
-      <c r="C16" s="141"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="143"/>
+      <c r="R15" s="141" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="111"/>
+      <c r="B16" s="112"/>
+      <c r="C16" s="144"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
+      <c r="F16" s="146"/>
       <c r="G16" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H16" s="28" t="s">
         <v>46</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="J16" s="123"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="142"/>
-      <c r="M16" s="142"/>
-      <c r="N16" s="143"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="144"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="136" t="s">
-        <v>181</v>
-      </c>
-      <c r="B17" s="137"/>
-      <c r="C17" s="138" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
+        <v>169</v>
+      </c>
+      <c r="J16" s="137"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="145"/>
+      <c r="M16" s="145"/>
+      <c r="N16" s="146"/>
+      <c r="O16" s="102"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="147"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="125" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="126"/>
+      <c r="C17" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
       <c r="G17" s="33" t="s">
         <v>45</v>
       </c>
@@ -6246,41 +6748,32 @@
         <v>46</v>
       </c>
       <c r="I17" s="32" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J17" s="70" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" s="140" t="s">
-        <v>98</v>
-      </c>
-      <c r="L17" s="140"/>
-      <c r="M17" s="140"/>
-      <c r="N17" s="140"/>
+        <v>84</v>
+      </c>
+      <c r="K17" s="143" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="143"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="143"/>
       <c r="O17" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q17" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="P17" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q17" s="23" t="s">
-        <v>185</v>
-      </c>
       <c r="R17" s="25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B3:P3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="C13:F14"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="O13:P13"/>
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="A17:B17"/>
@@ -6294,6 +6787,15 @@
     <mergeCell ref="P15:P16"/>
     <mergeCell ref="Q15:Q16"/>
     <mergeCell ref="R15:R16"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="C13:F14"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="O13:P13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{CE2D2DDE-B743-424E-B948-A5418C328A01}"/>
@@ -6310,8 +6812,8 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE54DA62-EEA8-422B-812C-80FE73AEAA7A}">
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -6335,73 +6837,73 @@
     <col min="20" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="82" t="str">
         <f>'Listado Objetos de Dominio'!$A$8</f>
         <v>Estímulo</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" thickBot="1">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="139" t="str">
+      <c r="B3" s="128" t="str">
         <f>'Listado Objetos de Dominio'!$B$8</f>
         <v>Elementos únicos de cada nivel para que el estudiante interactúe con las tareas</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="139"/>
-      <c r="O3" s="139"/>
-      <c r="P3" s="139"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>29</v>
       </c>
@@ -6455,11 +6957,11 @@
         <v>crearEstimulo</v>
       </c>
       <c r="R4" s="29" t="str">
-        <f>A25</f>
+        <f>A24</f>
         <v>eliminarEstimulo</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>45</v>
       </c>
@@ -6478,7 +6980,9 @@
       <c r="H5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="148" t="s">
+        <v>47</v>
+      </c>
       <c r="J5" s="12"/>
       <c r="K5" s="11" t="s">
         <v>48</v>
@@ -6496,34 +7000,32 @@
         <v>48</v>
       </c>
       <c r="P5" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="R5" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="Q5" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="R5" s="22" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C6" s="4">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="12"/>
       <c r="K6" s="11" t="s">
@@ -6542,44 +7044,42 @@
         <v>49</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R6" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4">
-        <v>36</v>
-      </c>
-      <c r="D7" s="4">
-        <v>36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
       <c r="J7" s="12"/>
       <c r="K7" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>49</v>
@@ -6588,18 +7088,18 @@
         <v>49</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="Q7" s="28" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="R7" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>46</v>
@@ -6634,18 +7134,18 @@
         <v>49</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q8" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R8" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>46</v>
@@ -6680,21 +7180,21 @@
         <v>49</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q9" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R9" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -6705,7 +7205,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="11" t="s">
@@ -6724,31 +7224,33 @@
         <v>49</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q10" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R10" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1500</v>
+      </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="4">
-        <v>25</v>
-      </c>
+      <c r="G11" s="4"/>
       <c r="H11" s="4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
@@ -6768,90 +7270,90 @@
         <v>49</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q11" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R11" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="13" spans="1:18">
-      <c r="A13" s="95" t="s">
+    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="85"/>
+      <c r="C13" s="86"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>67</v>
-      </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="97"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="16" t="s">
-        <v>68</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="66" customHeight="1" thickBot="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="46" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="15.75" thickBot="1"/>
-    <row r="17" spans="1:18">
-      <c r="A17" s="98" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="88"/>
+      <c r="C17" s="88" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82" t="s">
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82" t="s">
+      <c r="K17" s="88"/>
+      <c r="L17" s="88"/>
+      <c r="M17" s="88"/>
+      <c r="N17" s="88"/>
+      <c r="O17" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82" t="s">
+      <c r="P17" s="88"/>
+      <c r="Q17" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="82" t="s">
+      <c r="R17" s="95"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="89"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="R17" s="83"/>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="99"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="18" t="s">
+      <c r="H18" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>79</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>3</v>
@@ -6859,36 +7361,36 @@
       <c r="J18" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="84" t="s">
+      <c r="K18" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="84"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
       <c r="O18" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P18" s="18" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R18" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="R18" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="113" t="s">
-        <v>201</v>
-      </c>
-      <c r="B19" s="114"/>
-      <c r="C19" s="127" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="128"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="129"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="107" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="108"/>
+      <c r="C19" s="129" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="131"/>
       <c r="G19" s="19" t="s">
         <v>57</v>
       </c>
@@ -6896,231 +7398,203 @@
         <v>46</v>
       </c>
       <c r="I19" s="47" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="122" t="s">
-        <v>85</v>
-      </c>
-      <c r="K19" s="127" t="s">
-        <v>177</v>
-      </c>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="129"/>
+        <v>187</v>
+      </c>
+      <c r="J19" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="129" t="s">
+        <v>175</v>
+      </c>
+      <c r="L19" s="130"/>
+      <c r="M19" s="130"/>
+      <c r="N19" s="131"/>
       <c r="O19" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q19" s="89" t="s">
-        <v>205</v>
-      </c>
-      <c r="R19" s="133" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="115"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="132"/>
+        <v>201</v>
+      </c>
+      <c r="Q19" s="100" t="s">
+        <v>202</v>
+      </c>
+      <c r="R19" s="141" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="109"/>
+      <c r="B20" s="110"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="134"/>
       <c r="G20" s="19" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="H20" s="28" t="s">
         <v>46</v>
       </c>
       <c r="I20" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="J20" s="126"/>
-      <c r="K20" s="130"/>
-      <c r="L20" s="131"/>
-      <c r="M20" s="131"/>
-      <c r="N20" s="132"/>
+        <v>189</v>
+      </c>
+      <c r="J20" s="140"/>
+      <c r="K20" s="132"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133"/>
+      <c r="N20" s="134"/>
       <c r="O20" s="19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P20" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="134"/>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21" s="115"/>
-      <c r="B21" s="116"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="132"/>
+        <v>204</v>
+      </c>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="142"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="109"/>
+      <c r="B21" s="110"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="134"/>
       <c r="G21" s="19" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="H21" s="28" t="s">
         <v>46</v>
       </c>
       <c r="I21" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="J21" s="140"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="133"/>
+      <c r="N21" s="134"/>
+      <c r="O21" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q21" s="101" t="s">
+        <v>208</v>
+      </c>
+      <c r="R21" s="142"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="109"/>
+      <c r="B22" s="110"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="J21" s="126"/>
-      <c r="K21" s="130"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="P21" s="19" t="s">
+      <c r="J22" s="140"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="134"/>
+      <c r="O22" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="134"/>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="115"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="19" t="s">
+      <c r="P22" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="142"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="111"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="H23" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="137"/>
+      <c r="K23" s="144"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="P23" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q23" s="102"/>
+      <c r="R23" s="147"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="125" t="s">
+        <v>213</v>
+      </c>
+      <c r="B24" s="126"/>
+      <c r="C24" s="127" t="s">
+        <v>214</v>
+      </c>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="I22" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="J22" s="126"/>
-      <c r="K22" s="130"/>
-      <c r="L22" s="131"/>
-      <c r="M22" s="131"/>
-      <c r="N22" s="132"/>
-      <c r="O22" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="P22" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q22" s="90" t="s">
-        <v>213</v>
-      </c>
-      <c r="R22" s="134"/>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="115"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="J23" s="126"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="131"/>
-      <c r="M23" s="131"/>
-      <c r="N23" s="132"/>
-      <c r="O23" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="P23" s="19" t="s">
+      <c r="I24" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="127" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" s="127"/>
+      <c r="M24" s="127"/>
+      <c r="N24" s="127"/>
+      <c r="O24" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="Q23" s="135"/>
-      <c r="R23" s="134"/>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="117"/>
-      <c r="B24" s="118"/>
-      <c r="C24" s="141"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="I24" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="J24" s="123"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="142"/>
-      <c r="M24" s="142"/>
-      <c r="N24" s="143"/>
-      <c r="O24" s="19" t="s">
+      <c r="P24" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q24" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="P24" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q24" s="91"/>
-      <c r="R24" s="144"/>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="136" t="s">
-        <v>218</v>
-      </c>
-      <c r="B25" s="137"/>
-      <c r="C25" s="138" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="138"/>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K25" s="138" t="s">
-        <v>98</v>
-      </c>
-      <c r="L25" s="138"/>
-      <c r="M25" s="138"/>
-      <c r="N25" s="138"/>
-      <c r="O25" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="P25" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q25" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="R25" s="25" t="s">
-        <v>102</v>
+      <c r="R24" s="25" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="C19:F24"/>
-    <mergeCell ref="A19:B24"/>
+    <mergeCell ref="Q21:Q23"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="J19:J23"/>
+    <mergeCell ref="K19:N23"/>
+    <mergeCell ref="R19:R23"/>
+    <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="B3:P3"/>
@@ -7130,22 +7604,20 @@
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="J17:N17"/>
     <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q22:Q24"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="J19:J24"/>
-    <mergeCell ref="K19:N24"/>
-    <mergeCell ref="R19:R24"/>
-    <mergeCell ref="Q19:Q21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="C19:F23"/>
+    <mergeCell ref="A19:B23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="'Objetos de Dominio'!A1" display="Volver al inicio" xr:uid="{5C7EEABE-C166-4A7A-B335-4D5DB0D857BF}"/>
     <hyperlink ref="R4" location="Estimulo!A25" display="Estimulo!A25" xr:uid="{FF9BED0D-5076-480C-B497-7A50AF5B4F3D}"/>
-    <hyperlink ref="A25:B25" location="Estimulo!R4" display="eliminarEstimulo" xr:uid="{C46835F4-691D-4B4B-B66D-948914388D9F}"/>
+    <hyperlink ref="A24:B24" location="Estimulo!R4" display="eliminarEstimulo" xr:uid="{C46835F4-691D-4B4B-B66D-948914388D9F}"/>
     <hyperlink ref="A19:B19" location="'Objeto Dominio N'!Q4" display="Reponsabilidad 1" xr:uid="{68E21B7A-D701-418B-A186-3BCF686EE369}"/>
     <hyperlink ref="Q4" location="Estimulo!A19" display="Estimulo!A19" xr:uid="{B83769BA-2288-4092-BF8C-C7B50462A6E9}"/>
     <hyperlink ref="A1:P1" location="'Listado Objetos de Dominio'!A1" display="&lt;-Volver al inicio" xr:uid="{FCF2F2F0-27BF-46AB-9E26-25819BC60148}"/>
-    <hyperlink ref="A19:B23" location="Estimulo!Q4" display="crearEstimulo" xr:uid="{299D5D77-AAC3-4B12-B7E8-A66BC72BF1BC}"/>
+    <hyperlink ref="A19:B22" location="Estimulo!Q4" display="crearEstimulo" xr:uid="{299D5D77-AAC3-4B12-B7E8-A66BC72BF1BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7163,15 +7635,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100339E364CF2FAC646913FA2F6AF72DBE1" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b24b9c618f26a7f5898de1c13fded6f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d3168a39-8cd2-49bc-b1c5-42f933dcfd23" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1b230ff9972fda723d9ad96722259e8e" ns2:_="">
     <xsd:import namespace="d3168a39-8cd2-49bc-b1c5-42f933dcfd23"/>
@@ -7349,16 +7812,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2038022-656B-4A1B-A485-51A1972238BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2038022-656B-4A1B-A485-51A1972238BD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d3168a39-8cd2-49bc-b1c5-42f933dcfd23"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6724C681-8A04-4D66-BB1C-57F7466573C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A13C049B-ED9D-485F-97D0-84BB12CBD503}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d3168a39-8cd2-49bc-b1c5-42f933dcfd23"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A13C049B-ED9D-485F-97D0-84BB12CBD503}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6724C681-8A04-4D66-BB1C-57F7466573C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
